--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEW_MEXICO_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEW_MEXICO_2012.xlsx
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C112">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C162">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C194">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C523">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C555">
